--- a/data/trans_dic/P33_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P33_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,92; 21,09</t>
+          <t>12,2; 21,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 31,4</t>
+          <t>21,14; 31,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,3; 39,15</t>
+          <t>27,86; 39,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,21; 37,12</t>
+          <t>26,0; 36,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 20,93</t>
+          <t>11,77; 21,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,78; 42,08</t>
+          <t>30,09; 41,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,02; 42,46</t>
+          <t>31,44; 43,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,8; 40,06</t>
+          <t>29,37; 37,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,13; 19,65</t>
+          <t>12,75; 19,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,42; 35,35</t>
+          <t>27,06; 35,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,85; 39,02</t>
+          <t>30,3; 38,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,21; 36,78</t>
+          <t>28,72; 35,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,94; 27,25</t>
+          <t>19,81; 27,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,95; 32,21</t>
+          <t>23,45; 32,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,8; 30,93</t>
+          <t>22,56; 30,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,11; 33,74</t>
+          <t>22,58; 32,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 38,62</t>
+          <t>29,93; 38,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,78; 39,74</t>
+          <t>30,94; 39,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,65; 41,09</t>
+          <t>32,51; 40,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,35; 34,68</t>
+          <t>27,26; 34,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,16; 32,17</t>
+          <t>26,15; 31,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,81; 34,88</t>
+          <t>28,5; 34,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,67; 34,57</t>
+          <t>28,97; 34,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,31; 32,83</t>
+          <t>26,06; 32,45</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 17,25</t>
+          <t>9,02; 17,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,79; 35,44</t>
+          <t>25,07; 35,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,18; 16,52</t>
+          <t>9,64; 16,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,41; 31,25</t>
+          <t>22,34; 32,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,97; 25,09</t>
+          <t>16,18; 25,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,66; 38,27</t>
+          <t>27,23; 37,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 26,13</t>
+          <t>17,21; 26,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,38; 35,74</t>
+          <t>27,79; 35,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 19,67</t>
+          <t>14,07; 19,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,65; 34,94</t>
+          <t>27,42; 34,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,52; 20,52</t>
+          <t>14,91; 20,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,87; 32,02</t>
+          <t>26,48; 32,76</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,78; 16,95</t>
+          <t>9,57; 17,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,87; 36,97</t>
+          <t>27,15; 37,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,1; 39,2</t>
+          <t>29,33; 39,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,61; 33,38</t>
+          <t>22,41; 33,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,8; 22,58</t>
+          <t>14,4; 22,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,39; 50,17</t>
+          <t>38,77; 49,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,75; 47,14</t>
+          <t>36,7; 47,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,48; 39,01</t>
+          <t>34,26; 43,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 18,76</t>
+          <t>13,26; 18,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,06; 42,07</t>
+          <t>34,84; 42,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,47; 41,9</t>
+          <t>34,62; 41,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,03; 33,8</t>
+          <t>29,82; 37,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 31,85</t>
+          <t>19,73; 31,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,87; 38,0</t>
+          <t>24,92; 37,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,76</t>
+          <t>4,52; 12,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,77; 40,58</t>
+          <t>27,55; 38,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,29; 36,26</t>
+          <t>23,14; 36,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,66; 47,04</t>
+          <t>33,8; 46,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 12,97</t>
+          <t>5,03; 12,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,64; 49,34</t>
+          <t>39,52; 48,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,29; 31,68</t>
+          <t>22,99; 31,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,72; 40,82</t>
+          <t>31,2; 40,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 11,16</t>
+          <t>5,67; 11,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,42; 43,7</t>
+          <t>35,64; 42,74</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,87; 20,83</t>
+          <t>11,88; 20,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,64; 30,28</t>
+          <t>20,39; 30,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,56; 25,28</t>
+          <t>15,67; 25,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,35; 27,54</t>
+          <t>19,56; 28,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,07; 29,16</t>
+          <t>19,13; 29,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,76; 33,98</t>
+          <t>23,11; 33,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,31; 37,16</t>
+          <t>25,69; 36,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,46; 39,73</t>
+          <t>31,05; 40,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,66; 23,24</t>
+          <t>16,66; 23,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22,99; 30,48</t>
+          <t>23,12; 30,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,76; 29,43</t>
+          <t>21,64; 29,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,51; 31,88</t>
+          <t>26,33; 32,9</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,65; 18,65</t>
+          <t>12,62; 18,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,49</t>
+          <t>18,21; 25,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,31; 30,61</t>
+          <t>23,28; 30,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,0; 35,48</t>
+          <t>26,31; 33,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,16; 27,2</t>
+          <t>20,46; 26,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,42; 32,42</t>
+          <t>25,27; 32,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,79; 34,1</t>
+          <t>26,96; 34,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,33; 75,33</t>
+          <t>33,3; 39,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,2; 21,98</t>
+          <t>17,16; 21,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,67; 27,66</t>
+          <t>22,92; 27,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26,18; 31,29</t>
+          <t>26,12; 31,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,03; 63,83</t>
+          <t>30,84; 36,0</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,65; 25,56</t>
+          <t>19,72; 26,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,85; 25,83</t>
+          <t>19,81; 26,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,15; 21,84</t>
+          <t>16,25; 22,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,19; 12,33</t>
+          <t>8,99; 13,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,68; 27,16</t>
+          <t>20,78; 27,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,1; 29,67</t>
+          <t>23,12; 29,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,59; 23,72</t>
+          <t>17,38; 23,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,01; 16,25</t>
+          <t>12,22; 16,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,12; 25,52</t>
+          <t>21,22; 25,66</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,32; 26,83</t>
+          <t>22,54; 26,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,59; 21,56</t>
+          <t>17,49; 21,62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 13,43</t>
+          <t>11,19; 14,24</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,19; 20,02</t>
+          <t>17,16; 20,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24,38; 27,59</t>
+          <t>24,21; 27,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21,51; 24,65</t>
+          <t>21,7; 24,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,66; 25,73</t>
+          <t>22,96; 26,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,67; 25,58</t>
+          <t>22,68; 25,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,97; 34,37</t>
+          <t>30,84; 34,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,96; 30,1</t>
+          <t>26,98; 30,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29,45; 46,78</t>
+          <t>29,43; 32,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,39; 22,39</t>
+          <t>20,32; 22,3</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28,05; 30,32</t>
+          <t>28,27; 30,45</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24,85; 27,06</t>
+          <t>24,81; 27,04</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25,42; 35,64</t>
+          <t>26,65; 28,7</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96882</t>
+          <t>98726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>101392</t>
+          <t>106339</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>198274</t>
+          <t>205065</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32021; 56660</t>
+          <t>32775; 57097</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61050; 92148</t>
+          <t>62024; 92554</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79776; 114374</t>
+          <t>81410; 116567</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78527; 115605</t>
+          <t>82911; 116028</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29452; 54000</t>
+          <t>30373; 55069</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85253; 120458</t>
+          <t>86128; 119281</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87927; 120359</t>
+          <t>89124; 122311</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>89210; 116041</t>
+          <t>92834; 119718</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69138; 103483</t>
+          <t>67150; 102782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158962; 204915</t>
+          <t>156838; 202899</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>177585; 224597</t>
+          <t>174445; 221226</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>175578; 221064</t>
+          <t>182351; 224663</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117627</t>
+          <t>119903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>136741</t>
+          <t>146228</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>254368</t>
+          <t>266131</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98296; 134352</t>
+          <t>97692; 134997</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>120361; 161837</t>
+          <t>117815; 161702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114574; 155449</t>
+          <t>113360; 153620</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97811; 142813</t>
+          <t>98240; 141605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>151719; 193896</t>
+          <t>150247; 192510</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>161203; 208152</t>
+          <t>162048; 208284</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>170783; 214946</t>
+          <t>170033; 214349</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>121023; 153443</t>
+          <t>128034; 163395</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>260329; 320154</t>
+          <t>260220; 316501</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>295652; 357919</t>
+          <t>292521; 354399</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>294023; 354549</t>
+          <t>297119; 358426</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>227720; 284215</t>
+          <t>235838; 293617</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81943</t>
+          <t>84812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>108945</t>
+          <t>112231</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>190888</t>
+          <t>197043</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28411; 54167</t>
+          <t>28322; 54328</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79583; 113763</t>
+          <t>80480; 114068</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29233; 52612</t>
+          <t>30721; 53503</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67128; 98005</t>
+          <t>70043; 100685</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52920; 83152</t>
+          <t>53633; 83611</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94329; 130505</t>
+          <t>92849; 127358</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58587; 87885</t>
+          <t>57882; 87661</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94647; 123555</t>
+          <t>97894; 125845</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89719; 126941</t>
+          <t>90833; 127066</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183062; 231354</t>
+          <t>181530; 230474</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95069; 134364</t>
+          <t>97652; 134822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>170571; 211123</t>
+          <t>176317; 218101</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81591</t>
+          <t>101522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>139419</t>
+          <t>155799</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>221010</t>
+          <t>257322</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34145; 59166</t>
+          <t>33395; 59811</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100472; 138266</t>
+          <t>101538; 138809</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>107428; 144696</t>
+          <t>108268; 145678</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66384; 102571</t>
+          <t>82183; 124540</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54992; 83868</t>
+          <t>53481; 82880</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>152764; 194533</t>
+          <t>150359; 192945</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>140357; 180043</t>
+          <t>140182; 180450</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89039; 178284</t>
+          <t>137649; 173893</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93955; 135148</t>
+          <t>95535; 134851</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>267047; 320504</t>
+          <t>265400; 320825</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>258939; 314724</t>
+          <t>260027; 315348</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>160756; 258294</t>
+          <t>229163; 287504</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61689</t>
+          <t>67835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>94077</t>
+          <t>100787</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>155766</t>
+          <t>168622</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>40246; 64752</t>
+          <t>40105; 64804</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52881; 80793</t>
+          <t>52986; 80552</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9195; 24830</t>
+          <t>9547; 25870</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51425; 72537</t>
+          <t>56661; 78721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>48133; 74934</t>
+          <t>47824; 75578</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73617; 102880</t>
+          <t>73922; 102307</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11398; 28343</t>
+          <t>11000; 27568</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>84662; 102788</t>
+          <t>89661; 110764</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>95502; 129891</t>
+          <t>94243; 130710</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>136793; 176046</t>
+          <t>134568; 176429</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25296; 47951</t>
+          <t>24357; 47942</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>140971; 169158</t>
+          <t>154141; 184863</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62425</t>
+          <t>63193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>89630</t>
+          <t>92602</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>152054</t>
+          <t>155795</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31929; 56011</t>
+          <t>31943; 55693</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56538; 82952</t>
+          <t>55859; 84636</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40944; 66512</t>
+          <t>41223; 66292</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52187; 74270</t>
+          <t>52941; 76646</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52658; 80527</t>
+          <t>52822; 80618</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66522; 95154</t>
+          <t>64716; 93897</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68875; 101124</t>
+          <t>69906; 98940</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>78184; 101982</t>
+          <t>81772; 105331</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>90782; 126693</t>
+          <t>90791; 128948</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>127387; 168843</t>
+          <t>128090; 170012</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>116463; 157547</t>
+          <t>115821; 158943</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>134256; 167773</t>
+          <t>140603; 175704</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194108</t>
+          <t>215948</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>440070</t>
+          <t>280607</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>634178</t>
+          <t>496555</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>76650; 112991</t>
+          <t>76483; 114310</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>117777; 161599</t>
+          <t>120152; 165017</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>152035; 199606</t>
+          <t>151857; 199533</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>168543; 221501</t>
+          <t>189348; 243114</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>127986; 172676</t>
+          <t>129899; 171335</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>176031; 224520</t>
+          <t>175049; 227152</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>184648; 235062</t>
+          <t>185837; 235438</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>298318; 636018</t>
+          <t>254448; 304647</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>213446; 272763</t>
+          <t>212895; 270588</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306670; 374101</t>
+          <t>309947; 375878</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>351255; 419711</t>
+          <t>350446; 416580</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>485087; 937487</t>
+          <t>457605; 534117</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78437</t>
+          <t>88307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>100722</t>
+          <t>118480</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>179159</t>
+          <t>206787</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>142768; 185766</t>
+          <t>143273; 189044</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>154037; 200451</t>
+          <t>153787; 204421</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>125773; 170072</t>
+          <t>126492; 171658</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38926; 114531</t>
+          <t>71782; 107144</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>160623; 210943</t>
+          <t>161412; 211499</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>189172; 242943</t>
+          <t>189332; 243249</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>145165; 195723</t>
+          <t>143404; 191942</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>85827; 116093</t>
+          <t>101321; 138495</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>317439; 383567</t>
+          <t>319054; 385745</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>355970; 427919</t>
+          <t>359461; 427195</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>282086; 345673</t>
+          <t>280510; 346733</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>112337; 220666</t>
+          <t>182112; 231834</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>774702</t>
+          <t>840246</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1210995</t>
+          <t>1113074</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1985697</t>
+          <t>1953320</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>555227; 646675</t>
+          <t>554047; 649763</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>832387; 941945</t>
+          <t>826532; 934936</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>728777; 834909</t>
+          <t>735103; 838273</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>592845; 863876</t>
+          <t>787282; 894029</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>760929; 858862</t>
+          <t>761366; 861081</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1099157; 1219663</t>
+          <t>1094611; 1216383</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>951601; 1062651</t>
+          <t>952532; 1062267</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1047790; 1664509</t>
+          <t>1066597; 1169690</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1342973; 1474587</t>
+          <t>1338686; 1468943</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1952772; 2111054</t>
+          <t>1968252; 2120077</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1718801; 1871601</t>
+          <t>1716459; 1870789</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1757557; 2464388</t>
+          <t>1879397; 2023902</t>
         </is>
       </c>
     </row>
